--- a/data/trans_bre/P57_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P57_R2-Habitat-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 1,23</t>
+          <t>-8,18; 1,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 3,37</t>
+          <t>-7,46; 3,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 4,49</t>
+          <t>-25,46; 4,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 8,56</t>
+          <t>-16,06; 8,13</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 0,83</t>
+          <t>-7,06; 1,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,86; -5,66</t>
+          <t>-35,1; -5,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 3,09</t>
+          <t>-22,6; 4,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-48,02; -11,64</t>
+          <t>-46,24; -11,18</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 0,46</t>
+          <t>-9,64; -0,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-34,91; -5,07</t>
+          <t>-36,28; -5,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 1,64</t>
+          <t>-29,02; -0,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-63,22; -9,85</t>
+          <t>-64,79; -11,01</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -1,11</t>
+          <t>-9,08; -0,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,04; -2,33</t>
+          <t>-14,62; -2,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,65; -3,43</t>
+          <t>-27,35; -3,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,0; -6,23</t>
+          <t>-34,26; -6,7</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,2; -1,85</t>
+          <t>-6,38; -1,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-27,7; -7,58</t>
+          <t>-23,38; -6,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,64; -6,15</t>
+          <t>-20,02; -6,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-45,02; -16,0</t>
+          <t>-41,26; -13,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P57_R2-Habitat-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-2,06</t>
+          <t>-2,03</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,84%</t>
+          <t>-4,83%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,41</t>
+          <t>-8,49; 1,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 3,21</t>
+          <t>-7,09; 3,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 4,72</t>
+          <t>-26,19; 6,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 8,13</t>
+          <t>-15,84; 9,03</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-17,49</t>
+          <t>-7,32</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-29,23%</t>
+          <t>-14,95%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 1,24</t>
+          <t>-6,61; 1,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,1; -5,38</t>
+          <t>-11,76; -2,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 4,51</t>
+          <t>-21,17; 4,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,24; -11,18</t>
+          <t>-22,78; -5,71</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-18,28</t>
+          <t>-4,56</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-33,48%</t>
+          <t>-8,53%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,64; -0,23</t>
+          <t>-9,62; -0,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-36,28; -5,84</t>
+          <t>-9,91; 0,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,02; -0,74</t>
+          <t>-29,83; -0,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-64,79; -11,01</t>
+          <t>-17,75; 0,45</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-7,37</t>
+          <t>-4,88</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-17,81%</t>
+          <t>-11,91%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,08; -0,82</t>
+          <t>-9,28; -0,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -2,42</t>
+          <t>-9,58; -0,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,35; -3,06</t>
+          <t>-26,89; -2,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,26; -6,7</t>
+          <t>-21,59; -1,7</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-12,7</t>
+          <t>-5,17</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-25,08%</t>
+          <t>-11,14%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,38; -1,99</t>
+          <t>-6,08; -1,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,38; -6,57</t>
+          <t>-7,6; -2,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,02; -6,6</t>
+          <t>-19,39; -5,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-41,26; -13,9</t>
+          <t>-16,07; -6,13</t>
         </is>
       </c>
     </row>
